--- a/CJAP_Robot_Project_Plan_v2.xlsx
+++ b/CJAP_Robot_Project_Plan_v2.xlsx
@@ -1129,7 +1129,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="31">
       <c r="A4" s="39" t="inlineStr">
         <is>
@@ -2145,7 +2144,7 @@
       </c>
       <c r="K23" s="44" t="inlineStr">
         <is>
-          <t>Tracker W3.14 - Sponsor ratified bge-base-en-v1.5 @768d after a 4-candidate bake-off; bakeoff_FINAL_for_dok.md (2ca0255).</t>
+          <t>bge-base-en-v1.5 @768d ratified by the Sponsor at the 4-candidate bake-off; eval/results/arch_baseline_v4_retrieval.json records the anchor verbatim ("embedder = bge-base-en-v1.5, ratified by Dok") with recall_C_baseline. Alternatives archived WITH rollback, not deleted: data/index/_archived_bgelarge_*, _archived_pilotmm_*, bakeoff_bgebase/bgelarge_int8/minilm_*; bakeoff_FINAL_for_dok.md carries the scoring. Ratified before indexing. (verified 26 Sep 2026)</t>
         </is>
       </c>
     </row>
@@ -2199,12 +2198,12 @@
       </c>
       <c r="J24" s="44" t="inlineStr">
         <is>
-          <t>[~] Partial</t>
+          <t>[x] Done</t>
         </is>
       </c>
       <c r="K24" s="44" t="inlineStr">
         <is>
-          <t>data/index/corpus_dense.npy built at arch-baseline-v4.2. STALE since the batch-03 regenerate of 25 Sep - CE-6 full re-embed still to run.</t>
+          <t>REBUILT 26 Sep 2026 after batch-03 - no longer stale. data/index/corpus_dense.npy = (9804, 768) float32 unit-norm, BAAI/bge-base-en-v1.5, backend cuda_fp32, pilot_parity_sanity "skipped (no prior pilot index)". Provenance in corpus_dense_meta.json: model_id, dim, backend, normalize, batch_size, version_block (torch 2.5.1+cu121 / GTX 1650), n_chunks, build_date, chunk_index_sha256, chunk_ids. Model is a resident singleton (app/embeddings.get_model(), model_load_count stays 1) - loaded once, never per request. Runtime index rebuilt from it by scripts/make_runtime_dense_index.py (1,104 docs / 9,804 chunks).</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2258,12 @@
       </c>
       <c r="J25" s="44" t="inlineStr">
         <is>
-          <t>[x] Done</t>
+          <t>[~] Partial</t>
         </is>
       </c>
       <c r="K25" s="44" t="inlineStr">
         <is>
-          <t>Tracker W1.7 - data/index/topic_centroids.npy (34 centroids, built from scratch on the full corpus). Retag after CE-6 still pending (CE-7).</t>
+          <t>DOWNGRADED from Done, 26 Sep 2026 - two of five bullets are not met. MET: each topic carries label, definition, phrases, exemplars and matchers (corpus/voice/topic_map.json, 35 topics); full-corpus coverage and orphan census run against the corrected corpus (floor 0.68, 463/9,804 chunk-level orphans, 0/1,104 doc-level). NOT MET: (1) "every document tagged with a primary and secondary topic" - reports/w1_7_pilot_topic_tags.json covers 95 of 1,104 documents; merge_tag_topics.py's tagging step is hard-scoped to pilot_subset_frozen_v4.csv. (2) the independence check is mis-calibrated - at TOPIC_MERGE_COSINE 0.95 it collapsed 34 topics to 3 (220 of 561 pairs above threshold), so it was BYPASSED with CJ_TOPIC_MERGE_COSINE=1.01 and the v4.2 34-topic set restored (sha16 50600bdd34836db7, drift 2.98e-08). Related CE-8 defect: honors_received and robot_identity_meta are byte-identical zero-chunk centroids sharing one gmean fallback, and they are polluting secondary tags. See docs/p3/p3_3_recovery_2026-09-26.md.</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2317,12 @@
       </c>
       <c r="J26" s="44" t="inlineStr">
         <is>
-          <t>[~] Partial</t>
+          <t>[x] Done</t>
         </is>
       </c>
       <c r="K26" s="44" t="inlineStr">
         <is>
-          <t>Tracker W1.6 - BM25 + phrase dictionary. STALE for the same reason as P3.2; rebuild with build_sparse_index.py after CE-6.</t>
+          <t>REBUILT 26 Sep 2026 - no longer stale. data/index/pilot_sparse.pkl, BM25 over full chunk text, n_chunks 9,804 (was 9,865 pre-correction, including the 27 chunks of the 5 retired IDs). Curated keywords and entities kept atomic, never split: 9,497 phrases by provenance (keyword 4,006 / entity 4,854 / case 637) via the shared tokenizer in app/sparse.py. No chunk has zero terms (min doc_len 5). Retained alongside the dense arm as the plan requires. KNOWN DEFECT (CE-13/14, not a blocker): citations are indexed only as full-case-name atomic phrases, and "GR No." vs "G.R." tokenize differently - a bare docket-number query puts the right document at rank 31 of 9,804. Sized in docs/p3/phase6_c3_and_findings_2026-09-26.md.</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2381,7 @@
       </c>
       <c r="K27" s="44" t="inlineStr">
         <is>
-          <t>Tracker W2.4 - date index built and self-checked, but shipped dark (DATE_INDEX_ENABLED=false).</t>
+          <t>BUILT AND VERIFIED, STILL DARK. data/index/date_index.json rebuilt 26 Sep: 1,104 of 1,104 documents dated, 0 undated, precision day for all; sha256 82a550e6... identical before and after rebuild (deterministic). Dates come from the corpus front matter and the index is a date -&gt; document lookup. The relative-temporal resolver EXISTS: temporal_intent() at app/retrieval.py:221. Blocker to Done: config.DATE_INDEX_ENABLED = False, so none of it is live. Measured 26 Sep - enabling it via CJ_DATE_INDEX_ENABLED=1 flips CE-11 row X51 from FAIL to PASS at rank 5 and changes NO other row of the 14. Frozen-40 measurement pending (Phase 7 Part B) before the default is flipped. Note check_date_index.py's NO-REGRESSION GATE still compares against the bge-large arch_baseline_v2.json and mismatches all 40 by construction - batch-05 re-baseline.</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2441,7 @@
       </c>
       <c r="K28" s="44" t="inlineStr">
         <is>
-          <t>Voice Card / persona prefix live in the composer (tracker W2.3). Not found as a standalone reviewed persona_card.md.</t>
+          <t>Card is LIVE - corpus/voice/voice_card.md, 380 lines, loaded verbatim into the cached static prefix at app/answer_pipeline.py:534, so it is sent with every answer. MET: identity, register and refusal behaviour are all stated; length discipline is explicit (SS Length and register guidance - 60-100 words default, 20-40 for simple factual, up to 150 for doctrinal). NOT MET: (1) the opening block is FACTUALLY WRONG since W1.8 - it tells the model Haiku routed the question, that there are "no embeddings, no similarity search, no chunking", and that it received whole documents. The corrected header is staged at docs/p3/voice_card_header_proposed_2026-09-25.md (R-1) and deliberately unapplied until after CE-12 so the composer prefix and the corpus are not changed in the same run. (2) no signature-phrase palette section - one illustrative mention at line 353, not framed as an optional palette. (3) no authorship or review marker anywhere in the file - "written by the person who knows the voice" has not happened; the SME read is P3.6's outstanding item. Applying R-1 also needs a bge-base COMPOSE baseline, which may not exist. The Identity rule section is CORRECT and stays (decision D-042).</t>
         </is>
       </c>
     </row>
@@ -7077,12 +7076,12 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A28:J28"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A25:J25"/>
     <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A25:J25"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9730,8 +9729,8 @@
     <mergeCell ref="F32:H32"/>
     <mergeCell ref="F35:H35"/>
     <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A45:H45"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="C21:H21"/>
